--- a/infor-beta/templates/INFOR Ownership Template.xlsx
+++ b/infor-beta/templates/INFOR Ownership Template.xlsx
@@ -886,7 +886,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1224,6 +1224,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="14" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2099,7 +2105,7 @@
         <v>1</v>
       </c>
       <c r="B20" s="1">
-        <f>_xlfn.XLOOKUP(F20,$I$39:$I$178,$J$39:$J$178)</f>
+        <f>_xlfn.XLOOKUP(F20,$I$39:$I$185,$J$39:$J$185)</f>
         <v/>
       </c>
       <c r="F20" s="104">
@@ -2127,7 +2133,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="1">
-        <f>_xlfn.XLOOKUP(F21,$I$39:$I$178,$J$39:$J$178)</f>
+        <f>_xlfn.XLOOKUP(F21,$I$39:$I$185,$J$39:$J$185)</f>
         <v/>
       </c>
       <c r="F21" s="104">
@@ -2155,7 +2161,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="1">
-        <f>_xlfn.XLOOKUP(F22,$I$39:$I$178,$J$39:$J$178)</f>
+        <f>_xlfn.XLOOKUP(F22,$I$39:$I$185,$J$39:$J$185)</f>
         <v/>
       </c>
       <c r="F22" s="104">
@@ -2183,7 +2189,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="1">
-        <f>_xlfn.XLOOKUP(F23,$I$39:$I$178,$J$39:$J$178)</f>
+        <f>_xlfn.XLOOKUP(F23,$I$39:$I$185,$J$39:$J$185)</f>
         <v/>
       </c>
       <c r="F23" s="104">
@@ -2211,7 +2217,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="1">
-        <f>_xlfn.XLOOKUP(F24,$I$39:$I$178,$J$39:$J$178)</f>
+        <f>_xlfn.XLOOKUP(F24,$I$39:$I$185,$J$39:$J$185)</f>
         <v/>
       </c>
       <c r="F24" s="104">
@@ -2239,7 +2245,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="1">
-        <f>_xlfn.XLOOKUP(F25,$I$39:$I$178,$J$39:$J$178)</f>
+        <f>_xlfn.XLOOKUP(F25,$I$39:$I$185,$J$39:$J$185)</f>
         <v/>
       </c>
       <c r="F25" s="104">
@@ -2267,7 +2273,7 @@
         <v>7</v>
       </c>
       <c r="B26" s="1">
-        <f>_xlfn.XLOOKUP(F26,$I$39:$I$178,$J$39:$J$178)</f>
+        <f>_xlfn.XLOOKUP(F26,$I$39:$I$185,$J$39:$J$185)</f>
         <v/>
       </c>
       <c r="F26" s="104">
@@ -2295,7 +2301,7 @@
         <v>8</v>
       </c>
       <c r="B27" s="1">
-        <f>_xlfn.XLOOKUP(F27,$I$39:$I$178,$J$39:$J$178)</f>
+        <f>_xlfn.XLOOKUP(F27,$I$39:$I$185,$J$39:$J$185)</f>
         <v/>
       </c>
       <c r="F27" s="104">
@@ -2323,7 +2329,7 @@
         <v>9</v>
       </c>
       <c r="B28" s="1">
-        <f>_xlfn.XLOOKUP(F28,$I$39:$I$178,$J$39:$J$178)</f>
+        <f>_xlfn.XLOOKUP(F28,$I$39:$I$185,$J$39:$J$185)</f>
         <v/>
       </c>
       <c r="F28" s="104">
@@ -2351,7 +2357,7 @@
         <v>10</v>
       </c>
       <c r="B29" s="1">
-        <f>_xlfn.XLOOKUP(F29,$I$39:$I$178,$J$39:$J$178)</f>
+        <f>_xlfn.XLOOKUP(F29,$I$39:$I$185,$J$39:$J$185)</f>
         <v/>
       </c>
       <c r="F29" s="104">
@@ -2379,7 +2385,7 @@
         <v>11</v>
       </c>
       <c r="B30" s="1">
-        <f>_xlfn.XLOOKUP(F30,$I$39:$I$178,$J$39:$J$178)</f>
+        <f>_xlfn.XLOOKUP(F30,$I$39:$I$185,$J$39:$J$185)</f>
         <v/>
       </c>
       <c r="F30" s="104">
@@ -2407,7 +2413,7 @@
         <v>12</v>
       </c>
       <c r="B31" s="1">
-        <f>_xlfn.XLOOKUP(F31,$I$39:$I$178,$J$39:$J$178)</f>
+        <f>_xlfn.XLOOKUP(F31,$I$39:$I$185,$J$39:$J$185)</f>
         <v/>
       </c>
       <c r="F31" s="104">
@@ -2468,7 +2474,7 @@
       <c r="C33" s="58" t="n"/>
       <c r="D33" s="58" t="n"/>
       <c r="E33" s="58" t="n"/>
-      <c r="F33" s="100">
+      <c r="F33" s="139">
         <f>+F35-F32-F17</f>
         <v/>
       </c>
@@ -2516,7 +2522,7 @@
       <c r="C35" s="102" t="n"/>
       <c r="D35" s="102" t="n"/>
       <c r="E35" s="102" t="n"/>
-      <c r="F35" s="102" t="n"/>
+      <c r="F35" s="140" t="n"/>
       <c r="G35" s="103">
         <f>F35/$F$35</f>
         <v/>

--- a/infor-beta/templates/INFOR Ownership Template.xlsx
+++ b/infor-beta/templates/INFOR Ownership Template.xlsx
@@ -9,7 +9,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ownership" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloomberg Output" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="infor_own_bbg_link_block" localSheetId="0">'Ownership'!$H$68:$J$185</definedName>
+    <definedName name="infor_own_insider_block" localSheetId="0">'Ownership'!$B$39:$J$65</definedName>
+    <definedName name="infor_own_insiders_picture_range" localSheetId="0">'Ownership'!$B$4:$G$17</definedName>
+    <definedName name="infor_own_institutions_picture_range" localSheetId="0">'Ownership'!$B$19:$G$35</definedName>
+    <definedName name="infor_own_total_shares" localSheetId="0">'Ownership'!$F$35</definedName>
+    <definedName name="infor_own_bbg_holder_block" localSheetId="1">'Bloomberg Output'!$C$14:$AC$131</definedName>
+  </definedNames>
   <calcPr calcId="191029" calcMode="manual" fullCalcOnLoad="1" iterate="1"/>
 </workbook>
 </file>
